--- a/corrected-bank-specimens-for-user/16-acct430-test-data/parsed-excel/acct430 bank statement - parsed.xlsx
+++ b/corrected-bank-specimens-for-user/16-acct430-test-data/parsed-excel/acct430 bank statement - parsed.xlsx
@@ -426,7 +426,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-08T16:17:01.904Z</v>
+        <v>2026-07-14T13:50:04.660Z</v>
       </c>
     </row>
     <row r="5">

--- a/corrected-bank-specimens-for-user/16-acct430-test-data/parsed-excel/acct430 bank statement - parsed.xlsx
+++ b/corrected-bank-specimens-for-user/16-acct430-test-data/parsed-excel/acct430 bank statement - parsed.xlsx
@@ -426,7 +426,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-14T13:50:04.660Z</v>
+        <v>2026-07-17T19:29:58.391Z</v>
       </c>
     </row>
     <row r="5">
